--- a/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Diario Manager'!$A$1:$G$26</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Semanal Manager'!$A$1:$G$26</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mensual Manager'!$A$1:$G$26</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Handover Turno'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -140,44 +145,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -537,15 +558,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -553,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -560,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -567,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -574,8 +599,33 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -589,16 +639,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Diario del Manager</t>
@@ -612,10 +662,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -640,7 +691,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -657,10 +708,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -686,10 +735,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -715,10 +762,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -744,10 +789,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -780,10 +823,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -809,10 +850,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -838,10 +877,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -867,10 +904,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -903,10 +938,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -932,10 +965,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -961,10 +992,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -990,10 +1019,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1019,10 +1046,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1047,6 +1072,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -1055,14 +1081,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -1070,6 +1101,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -1087,7 +1119,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1102,16 +1144,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Semanal (Lunes)</t>
@@ -1125,10 +1167,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1153,7 +1196,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1170,10 +1213,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1199,10 +1240,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1228,10 +1267,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1257,10 +1294,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1293,10 +1328,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1322,10 +1355,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1351,10 +1382,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1380,10 +1409,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1409,10 +1436,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1438,10 +1463,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -1474,10 +1497,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1503,10 +1524,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1532,10 +1551,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1560,6 +1577,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -1568,14 +1586,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -1583,6 +1606,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -1600,7 +1624,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1615,16 +1649,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist Mensual</t>
@@ -1638,10 +1672,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1666,7 +1701,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1683,10 +1718,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1712,10 +1745,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1741,10 +1772,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1770,10 +1799,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1806,10 +1833,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1835,10 +1860,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1864,10 +1887,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1893,10 +1914,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1922,10 +1941,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1951,10 +1968,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -1987,10 +2002,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2016,10 +2029,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2045,10 +2056,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -2073,6 +2082,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -2081,14 +2091,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -2096,6 +2111,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -2113,7 +2129,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2128,16 +2154,16 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cambio de Turno</t>
@@ -2151,10 +2177,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2179,7 +2206,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2196,10 +2223,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2225,10 +2250,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -2254,10 +2277,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -2290,10 +2311,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -2319,10 +2338,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -2348,10 +2365,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2377,10 +2392,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -2413,10 +2426,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2442,10 +2453,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -2470,6 +2479,7 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="15" t="inlineStr">
         <is>
@@ -2478,14 +2488,19 @@
       </c>
       <c r="D18" s="16">
         <f>COUNTIF(F5:F16,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>de 9</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -2493,6 +2508,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -2510,7 +2526,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
@@ -14,9 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,7 +638,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1129,8 +1133,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1139,7 +1151,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1634,8 +1646,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1644,7 +1664,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2139,8 +2159,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2149,7 +2177,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2536,7 +2564,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/03-tareas-manager.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +139,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -151,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +207,49 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,58 +627,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Tareas del Manager / Encargado — Hamburguesería</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists de gestión para tu hamburguesería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Diario, semanal, mensual + handover de turno</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 03-tareas-manager.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -640,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -690,7 +857,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -705,431 +872,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DE ABRIR</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Revisar reservas/eventos del día</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Comprobar equipo completo</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Briefing: burger del día, 86s, promos, alérgenos</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Verificar stock: carne, pan, queso, patatas</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Supervisar tiempos: burger en &lt;12 min</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Controlar calidad: punto carne, presentación</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Gestionar delivery: tiempos y packaging correcto</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Resolver incidencias</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Supervisar cierre completo</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Cuadrar caja (efectivo + tarjeta + delivery)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Hacer pedidos mañana (carne, pan, patatas)</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Anotar incidencias y 86s del día</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y pausas)</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Cerrar: alarma, luces, gas</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="16">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1153,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1175,7 +1434,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1462,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1218,431 +1477,496 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANÁLISIS</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Revisar ventas semana (dine-in vs delivery vs take-away)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Analizar burgers más vendidas</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Revisar feedback: Google, apps delivery</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Evaluar desperdicio de carne y pan</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PEDIDOS</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Pedido carne (blend, angus, wagyu según carta)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Pedido pan burger (brioche, pretzel)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Pedido patatas (frescas o congeladas)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Pedido quesos y salsas</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Stock packaging delivery</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Stock limpieza</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Supervisar limpieza profunda</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Test aceite freidora (polares)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Verificar caducidades</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="16">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
+      <c r="F27">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
         <v>13.0</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1666,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1688,7 +2012,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1716,7 +2040,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1731,431 +2055,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  FINANCIERO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Revisar P&amp;L del mes</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Food cost (objetivo 28-32%)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Coste laboral vs facturación</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes (hay que conservarlos 4 años)</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Comisiones apps delivery</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Limpiar plancha a fondo (desmontar si es posible)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Cambiar aceite de freidora completo</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Lavavajillas: filtros, sal, abrillantador</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Campana: filtros</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Climatización: filtros</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Extintor y botiquín: verificar</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARKETING</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Evaluar carta: rotar burgers especiales</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Planificar promos del mes</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Fotos RRSS y apps delivery</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="16">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2179,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2229,7 +2645,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2244,323 +2660,388 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTADO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Mesas ocupadas y reservas pendientes</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Comandas en curso</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Pedidos delivery pendientes</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK</t>
         </is>
       </c>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Patties de carne restantes</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Pan de burger restante</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Estado del aceite de freidora</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>86s: qué se ha agotado</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  INCIDENCIAS</t>
         </is>
       </c>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Incidencias del turno</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Quejas de clientes</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
     <row r="18">
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D18" s="16">
-        <f>COUNTIF(F5:F16,"✓")</f>
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23" s="16">
+        <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F18">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G16">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
